--- a/etf_holdings/2026-10-13_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-13_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.39%2540</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2540</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.5%6150</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.5%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>6150</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.39%4625</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.39%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4625</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.18%1255</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.18%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1255</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.6%3385</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3385</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.07%7160</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7160</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.96%6130</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.96%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>6130</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.16%636</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.16%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>636</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.31%1900</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.31%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.9%2130</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.9%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>2130</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.37%1440</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.37%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1440</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.29%1735</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.29%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1735</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.36%145.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.36%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>145.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.56%2275</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.56%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2275</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:15</t>
+          <t>2026-10-13 02:11:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.21%2355</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2355</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:26</t>
+          <t>2026-10-13 02:11:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:37</t>
+          <t>2026-10-13 02:11:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:49</t>
+          <t>2026-10-13 02:11:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:49</t>
+          <t>2026-10-13 02:11:56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:49</t>
+          <t>2026-10-13 02:11:56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:49</t>
+          <t>2026-10-13 02:11:56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:49</t>
+          <t>2026-10-13 02:11:56</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-13 02:03:49</t>
+          <t>2026-10-13 02:11:56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-13_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-13_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:47</t>
+          <t>2026-10-13 03:01:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:53</t>
+          <t>2026-10-13 03:01:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:54</t>
+          <t>2026-10-13 03:01:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:56</t>
+          <t>2026-10-13 03:01:46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:56</t>
+          <t>2026-10-13 03:01:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:56</t>
+          <t>2026-10-13 03:01:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:56</t>
+          <t>2026-10-13 03:01:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:56</t>
+          <t>2026-10-13 03:01:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:56</t>
+          <t>2026-10-13 03:01:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
